--- a/data/XRD/2 Round/Mo_room_25Se_400Sb_35Se.xlsx
+++ b/data/XRD/2 Round/Mo_room_25Se_400Sb_35Se.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/XRD/2 Round/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE5F9A4-692B-4ADF-89A9-0F3D4325B998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{BAE5F9A4-692B-4ADF-89A9-0F3D4325B998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454376BA-2906-4ECF-87D4-7BF35E1D8DEC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD6B42E7-8F25-4A4F-8CC8-88E838C5844F}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{BD6B42E7-8F25-4A4F-8CC8-88E838C5844F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="388">
   <si>
     <t>No.</t>
   </si>
@@ -134,15 +134,9 @@
     <t>3,85</t>
   </si>
   <si>
-    <t>96-900-8581</t>
-  </si>
-  <si>
     <t>0,08(2)</t>
   </si>
   <si>
-    <t>96-901-3009</t>
-  </si>
-  <si>
     <t>100,00</t>
   </si>
   <si>
@@ -155,1000 +149,1042 @@
     <t>0,10(1)</t>
   </si>
   <si>
+    <t>0,11(1)</t>
+  </si>
+  <si>
+    <t>1,09</t>
+  </si>
+  <si>
+    <t>0,14(1)</t>
+  </si>
+  <si>
+    <t>0,118(9)</t>
+  </si>
+  <si>
+    <t>0,15(2)</t>
+  </si>
+  <si>
+    <t>0,0720</t>
+  </si>
+  <si>
+    <t>0,096000</t>
+  </si>
+  <si>
+    <t>152(14)</t>
+  </si>
+  <si>
+    <t>7,82</t>
+  </si>
+  <si>
+    <t>0,94</t>
+  </si>
+  <si>
+    <t>15,0002</t>
+  </si>
+  <si>
+    <t>37,41</t>
+  </si>
+  <si>
+    <t>3797,06</t>
+  </si>
+  <si>
+    <t>5,90142</t>
+  </si>
+  <si>
+    <t>389,72</t>
+  </si>
+  <si>
+    <t>4,14</t>
+  </si>
+  <si>
+    <t>16,746(3)</t>
+  </si>
+  <si>
+    <t>0,04(1)</t>
+  </si>
+  <si>
+    <t>21,76</t>
+  </si>
+  <si>
+    <t>2672,43</t>
+  </si>
+  <si>
+    <t>5,29006</t>
+  </si>
+  <si>
+    <t>363(61)</t>
+  </si>
+  <si>
+    <t>0,059959</t>
+  </si>
+  <si>
+    <t>16,833(2)</t>
+  </si>
+  <si>
+    <t>0,070(4)</t>
+  </si>
+  <si>
+    <t>61,12</t>
+  </si>
+  <si>
+    <t>2652,92</t>
+  </si>
+  <si>
+    <t>5,26284</t>
+  </si>
+  <si>
+    <t>824(35)</t>
+  </si>
+  <si>
+    <t>8,75</t>
+  </si>
+  <si>
+    <t>0,074155</t>
+  </si>
+  <si>
+    <t>23,867(2)</t>
+  </si>
+  <si>
+    <t>0,072(7)</t>
+  </si>
+  <si>
+    <t>55,97</t>
+  </si>
+  <si>
+    <t>1792,74</t>
+  </si>
+  <si>
+    <t>3,72525</t>
+  </si>
+  <si>
+    <t>492(31)</t>
+  </si>
+  <si>
+    <t>5,23</t>
+  </si>
+  <si>
+    <t>0,113696</t>
+  </si>
+  <si>
+    <t>27,006(3)</t>
+  </si>
+  <si>
+    <t>37,17</t>
+  </si>
+  <si>
+    <t>1545,76</t>
+  </si>
+  <si>
+    <t>3,29895</t>
+  </si>
+  <si>
+    <t>296(22)</t>
+  </si>
+  <si>
+    <t>3,15</t>
+  </si>
+  <si>
+    <t>0,125398</t>
+  </si>
+  <si>
+    <t>27,360(1)</t>
+  </si>
+  <si>
+    <t>0,078(4)</t>
+  </si>
+  <si>
+    <t>97,62</t>
+  </si>
+  <si>
+    <t>1518,37</t>
+  </si>
+  <si>
+    <t>3,25709</t>
+  </si>
+  <si>
+    <t>795(29)</t>
+  </si>
+  <si>
+    <t>8,45</t>
+  </si>
+  <si>
+    <t>0,122738</t>
+  </si>
+  <si>
+    <t>27,659(3)</t>
+  </si>
+  <si>
+    <t>86,27</t>
+  </si>
+  <si>
+    <t>1495,30</t>
+  </si>
+  <si>
+    <t>3,22257</t>
+  </si>
+  <si>
+    <t>466(23)</t>
+  </si>
+  <si>
+    <t>4,95</t>
+  </si>
+  <si>
+    <t>0,184936</t>
+  </si>
+  <si>
+    <t>28,1699(6)</t>
+  </si>
+  <si>
+    <t>0,077(2)</t>
+  </si>
+  <si>
+    <t>218,91</t>
+  </si>
+  <si>
+    <t>1456,04</t>
+  </si>
+  <si>
+    <t>3,16526</t>
+  </si>
+  <si>
+    <t>1851(34)</t>
+  </si>
+  <si>
+    <t>19,65</t>
+  </si>
+  <si>
+    <t>0,118284</t>
+  </si>
+  <si>
+    <t>31,1469(4)</t>
+  </si>
+  <si>
+    <t>0,092(1)</t>
+  </si>
+  <si>
+    <t>463,71</t>
+  </si>
+  <si>
+    <t>1237,79</t>
+  </si>
+  <si>
+    <t>2,86918</t>
+  </si>
+  <si>
+    <t>3590(32)</t>
+  </si>
+  <si>
+    <t>38,12</t>
+  </si>
+  <si>
+    <t>0,129170</t>
+  </si>
+  <si>
+    <t>32,1930(8)</t>
+  </si>
+  <si>
+    <t>0,076(1)</t>
+  </si>
+  <si>
+    <t>142,66</t>
+  </si>
+  <si>
+    <t>1169,37</t>
+  </si>
+  <si>
+    <t>2,77829</t>
+  </si>
+  <si>
+    <t>1191(20)</t>
+  </si>
+  <si>
+    <t>12,64</t>
+  </si>
+  <si>
+    <t>0,119828</t>
+  </si>
+  <si>
+    <t>33,104(2)</t>
+  </si>
+  <si>
+    <t>0,082(6)</t>
+  </si>
+  <si>
+    <t>49,89</t>
+  </si>
+  <si>
+    <t>1115,69</t>
+  </si>
+  <si>
+    <t>2,70389</t>
+  </si>
+  <si>
+    <t>444(22)</t>
+  </si>
+  <si>
+    <t>4,72</t>
+  </si>
+  <si>
+    <t>0,112251</t>
+  </si>
+  <si>
+    <t>34,0781(9)</t>
+  </si>
+  <si>
+    <t>0,078(3)</t>
+  </si>
+  <si>
+    <t>104,42</t>
+  </si>
+  <si>
+    <t>1066,09</t>
+  </si>
+  <si>
+    <t>2,62880</t>
+  </si>
+  <si>
+    <t>906(25)</t>
+  </si>
+  <si>
+    <t>9,62</t>
+  </si>
+  <si>
+    <t>0,115264</t>
+  </si>
+  <si>
+    <t>35,6068(8)</t>
+  </si>
+  <si>
+    <t>0,104(3)</t>
+  </si>
+  <si>
+    <t>147,44</t>
+  </si>
+  <si>
+    <t>1009,11</t>
+  </si>
+  <si>
+    <t>2,51936</t>
+  </si>
+  <si>
+    <t>1128(20)</t>
+  </si>
+  <si>
+    <t>11,97</t>
+  </si>
+  <si>
+    <t>0,130759</t>
+  </si>
+  <si>
+    <t>37,990(1)</t>
+  </si>
+  <si>
+    <t>0,111(3)</t>
+  </si>
+  <si>
+    <t>142,29</t>
+  </si>
+  <si>
+    <t>910,83</t>
+  </si>
+  <si>
+    <t>2,36661</t>
+  </si>
+  <si>
+    <t>981(24)</t>
+  </si>
+  <si>
+    <t>10,42</t>
+  </si>
+  <si>
+    <t>0,144987</t>
+  </si>
+  <si>
+    <t>38,7952(9)</t>
+  </si>
+  <si>
+    <t>0,115(2)</t>
+  </si>
+  <si>
+    <t>194,94</t>
+  </si>
+  <si>
+    <t>883,09</t>
+  </si>
+  <si>
+    <t>2,31933</t>
+  </si>
+  <si>
+    <t>1308(23)</t>
+  </si>
+  <si>
+    <t>13,88</t>
+  </si>
+  <si>
+    <t>0,149085</t>
+  </si>
+  <si>
+    <t>39,07(1)</t>
+  </si>
+  <si>
+    <t>0,07(4)</t>
+  </si>
+  <si>
+    <t>10,21</t>
+  </si>
+  <si>
+    <t>873,87</t>
+  </si>
+  <si>
+    <t>2,30339</t>
+  </si>
+  <si>
+    <t>119(676)</t>
+  </si>
+  <si>
+    <t>1,27</t>
+  </si>
+  <si>
+    <t>0,085506</t>
+  </si>
+  <si>
+    <t>39,451(5)</t>
+  </si>
+  <si>
+    <t>861,75</t>
+  </si>
+  <si>
+    <t>2,28230</t>
+  </si>
+  <si>
+    <t>0(690)</t>
+  </si>
+  <si>
+    <t>0,094547</t>
+  </si>
+  <si>
+    <t>40,3560(4)</t>
+  </si>
+  <si>
+    <t>0,3754(9)</t>
+  </si>
+  <si>
+    <t>4795,79</t>
+  </si>
+  <si>
+    <t>833,96</t>
+  </si>
+  <si>
+    <t>2,23315</t>
+  </si>
+  <si>
+    <t>9417(27)</t>
+  </si>
+  <si>
+    <t>0,509251</t>
+  </si>
+  <si>
+    <t>41,326(3)</t>
+  </si>
+  <si>
+    <t>0,164(9)</t>
+  </si>
+  <si>
+    <t>83,91</t>
+  </si>
+  <si>
+    <t>806,22</t>
+  </si>
+  <si>
+    <t>2,18297</t>
+  </si>
+  <si>
+    <t>385(18)</t>
+  </si>
+  <si>
+    <t>4,09</t>
+  </si>
+  <si>
+    <t>0,218042</t>
+  </si>
+  <si>
+    <t>0,13(3)</t>
+  </si>
+  <si>
+    <t>8,64</t>
+  </si>
+  <si>
+    <t>795,43</t>
+  </si>
+  <si>
+    <t>2,16311</t>
+  </si>
+  <si>
+    <t>50(12)</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0,173537</t>
+  </si>
+  <si>
+    <t>44,935(2)</t>
+  </si>
+  <si>
+    <t>0,157(6)</t>
+  </si>
+  <si>
+    <t>111,31</t>
+  </si>
+  <si>
+    <t>718,69</t>
+  </si>
+  <si>
+    <t>2,01567</t>
+  </si>
+  <si>
+    <t>533(18)</t>
+  </si>
+  <si>
+    <t>5,66</t>
+  </si>
+  <si>
+    <t>0,208909</t>
+  </si>
+  <si>
+    <t>45,103(4)</t>
+  </si>
+  <si>
+    <t>0,063(8)</t>
+  </si>
+  <si>
+    <t>23,38</t>
+  </si>
+  <si>
+    <t>715,14</t>
+  </si>
+  <si>
+    <t>2,00853</t>
+  </si>
+  <si>
+    <t>283(46)</t>
+  </si>
+  <si>
+    <t>3,01</t>
+  </si>
+  <si>
+    <t>0,082573</t>
+  </si>
+  <si>
+    <t>45,251(2)</t>
+  </si>
+  <si>
+    <t>0,036(6)</t>
+  </si>
+  <si>
+    <t>712,04</t>
+  </si>
+  <si>
+    <t>2,00230</t>
+  </si>
+  <si>
+    <t>218(36)</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>0,046763</t>
+  </si>
+  <si>
+    <t>45,42(1)</t>
+  </si>
+  <si>
+    <t>0,17(3)</t>
+  </si>
+  <si>
+    <t>44,82</t>
+  </si>
+  <si>
+    <t>708,65</t>
+  </si>
+  <si>
+    <t>1,99544</t>
+  </si>
+  <si>
+    <t>204(29)</t>
+  </si>
+  <si>
+    <t>2,16</t>
+  </si>
+  <si>
+    <t>0,220159</t>
+  </si>
+  <si>
+    <t>45,562(2)</t>
+  </si>
+  <si>
+    <t>0,079(8)</t>
+  </si>
+  <si>
+    <t>62,66</t>
+  </si>
+  <si>
+    <t>705,65</t>
+  </si>
+  <si>
+    <t>1,98936</t>
+  </si>
+  <si>
+    <t>603(54)</t>
+  </si>
+  <si>
+    <t>6,40</t>
+  </si>
+  <si>
+    <t>0,103977</t>
+  </si>
+  <si>
+    <t>45,982(5)</t>
+  </si>
+  <si>
+    <t>0,11(2)</t>
+  </si>
+  <si>
+    <t>22,94</t>
+  </si>
+  <si>
+    <t>697,24</t>
+  </si>
+  <si>
+    <t>1,97217</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>0,151181</t>
+  </si>
+  <si>
+    <t>48,925(8)</t>
+  </si>
+  <si>
+    <t>644,59</t>
+  </si>
+  <si>
+    <t>1,86019</t>
+  </si>
+  <si>
+    <t>71(9)</t>
+  </si>
+  <si>
+    <t>0,76</t>
+  </si>
+  <si>
+    <t>0,109831</t>
+  </si>
+  <si>
+    <t>49,62(1)</t>
+  </si>
+  <si>
+    <t>0,08(4)</t>
+  </si>
+  <si>
+    <t>5,80</t>
+  </si>
+  <si>
+    <t>633,65</t>
+  </si>
+  <si>
+    <t>1,83590</t>
+  </si>
+  <si>
+    <t>54(12)</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>0,107909</t>
+  </si>
+  <si>
+    <t>51,034(4)</t>
+  </si>
+  <si>
+    <t>28,71</t>
+  </si>
+  <si>
+    <t>612,68</t>
+  </si>
+  <si>
+    <t>1,78815</t>
+  </si>
+  <si>
+    <t>191(13)</t>
+  </si>
+  <si>
+    <t>2,02</t>
+  </si>
+  <si>
+    <t>0,150533</t>
+  </si>
+  <si>
+    <t>51,9247(7)</t>
+  </si>
+  <si>
+    <t>0,162(2)</t>
+  </si>
+  <si>
+    <t>402,92</t>
+  </si>
+  <si>
+    <t>600,44</t>
+  </si>
+  <si>
+    <t>1,75956</t>
+  </si>
+  <si>
+    <t>1961(17)</t>
+  </si>
+  <si>
+    <t>20,82</t>
+  </si>
+  <si>
+    <t>0,205507</t>
+  </si>
+  <si>
+    <t>52,153(5)</t>
+  </si>
+  <si>
+    <t>0,12(2)</t>
+  </si>
+  <si>
+    <t>27,75</t>
+  </si>
+  <si>
+    <t>597,41</t>
+  </si>
+  <si>
+    <t>1,75239</t>
+  </si>
+  <si>
+    <t>182(17)</t>
+  </si>
+  <si>
+    <t>1,93</t>
+  </si>
+  <si>
+    <t>0,152291</t>
+  </si>
+  <si>
+    <t>53,993(3)</t>
+  </si>
+  <si>
+    <t>45,55</t>
+  </si>
+  <si>
+    <t>574,45</t>
+  </si>
+  <si>
+    <t>1,69693</t>
+  </si>
+  <si>
+    <t>257(12)</t>
+  </si>
+  <si>
+    <t>2,73</t>
+  </si>
+  <si>
+    <t>0,177429</t>
+  </si>
+  <si>
+    <t>55,33(1)</t>
+  </si>
+  <si>
+    <t>8,65</t>
+  </si>
+  <si>
+    <t>559,20</t>
+  </si>
+  <si>
+    <t>1,65896</t>
+  </si>
+  <si>
+    <t>52(8)</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>0,166478</t>
+  </si>
+  <si>
+    <t>58,158(3)</t>
+  </si>
+  <si>
+    <t>0,226(6)</t>
+  </si>
+  <si>
+    <t>128,33</t>
+  </si>
+  <si>
+    <t>530,51</t>
+  </si>
+  <si>
+    <t>1,58494</t>
+  </si>
+  <si>
+    <t>422(12)</t>
+  </si>
+  <si>
+    <t>4,48</t>
+  </si>
+  <si>
+    <t>0,304233</t>
+  </si>
+  <si>
+    <t>61,121(2)</t>
+  </si>
+  <si>
+    <t>0,020(3)</t>
+  </si>
+  <si>
+    <t>4,84</t>
+  </si>
+  <si>
+    <t>504,39</t>
+  </si>
+  <si>
+    <t>1,51500</t>
+  </si>
+  <si>
+    <t>181(7)</t>
+  </si>
+  <si>
+    <t>1,92</t>
+  </si>
+  <si>
+    <t>0,026755</t>
+  </si>
+  <si>
+    <t>63,242(8)</t>
+  </si>
+  <si>
+    <t>0,22(2)</t>
+  </si>
+  <si>
+    <t>31,67</t>
+  </si>
+  <si>
+    <t>487,63</t>
+  </si>
+  <si>
+    <t>1,46920</t>
+  </si>
+  <si>
+    <t>110(9)</t>
+  </si>
+  <si>
+    <t>1,16</t>
+  </si>
+  <si>
+    <t>0,288959</t>
+  </si>
+  <si>
+    <t>66,185(6)</t>
+  </si>
+  <si>
+    <t>13,43</t>
+  </si>
+  <si>
+    <t>466,32</t>
+  </si>
+  <si>
+    <t>1,41082</t>
+  </si>
+  <si>
+    <t>95(12)</t>
+  </si>
+  <si>
+    <t>1,00</t>
+  </si>
+  <si>
+    <t>0,141915</t>
+  </si>
+  <si>
+    <t>69,023(6)</t>
+  </si>
+  <si>
+    <t>19,94</t>
+  </si>
+  <si>
+    <t>447,33</t>
+  </si>
+  <si>
+    <t>1,35959</t>
+  </si>
+  <si>
+    <t>103(9)</t>
+  </si>
+  <si>
+    <t>0,193647</t>
+  </si>
+  <si>
+    <t>71,759(4)</t>
+  </si>
+  <si>
+    <t>22,20</t>
+  </si>
+  <si>
+    <t>429,90</t>
+  </si>
+  <si>
+    <t>1,31431</t>
+  </si>
+  <si>
+    <t>147(14)</t>
+  </si>
+  <si>
+    <t>1,56</t>
+  </si>
+  <si>
+    <t>0,151518</t>
+  </si>
+  <si>
+    <t>73,492(4)</t>
+  </si>
+  <si>
+    <t>0,764(9)</t>
+  </si>
+  <si>
+    <t>566,28</t>
+  </si>
+  <si>
+    <t>419,13</t>
+  </si>
+  <si>
+    <t>1,28755</t>
+  </si>
+  <si>
+    <t>559(8)</t>
+  </si>
+  <si>
+    <t>5,94</t>
+  </si>
+  <si>
+    <t>1,012227</t>
+  </si>
+  <si>
+    <t>76(976)</t>
+  </si>
+  <si>
+    <t>1(8307)</t>
+  </si>
+  <si>
+    <t>405,99</t>
+  </si>
+  <si>
+    <t>1,25650</t>
+  </si>
+  <si>
+    <t>1(913)</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>1,488329</t>
+  </si>
+  <si>
+    <t>00-015-0861</t>
+  </si>
+  <si>
+    <t>00-029-0914</t>
+  </si>
+  <si>
+    <t>00-015-0861; 00-029-0914</t>
+  </si>
+  <si>
+    <t>63,4574</t>
+  </si>
+  <si>
+    <t>0,5751</t>
+  </si>
+  <si>
+    <t>79,75</t>
+  </si>
+  <si>
+    <t>486,00</t>
+  </si>
+  <si>
+    <t>1,46473</t>
+  </si>
+  <si>
+    <t>104,00</t>
+  </si>
+  <si>
+    <t>1,10</t>
+  </si>
+  <si>
+    <t>Manual input</t>
+  </si>
+  <si>
+    <t>0,766818</t>
+  </si>
+  <si>
+    <t>34,3592</t>
+  </si>
+  <si>
+    <t>0,0532</t>
+  </si>
+  <si>
+    <t>10,82</t>
+  </si>
+  <si>
+    <t>1053,53</t>
+  </si>
+  <si>
+    <t>2,60793</t>
+  </si>
+  <si>
+    <t>152,47</t>
+  </si>
+  <si>
+    <t>1,62</t>
+  </si>
+  <si>
+    <t>0,070963</t>
+  </si>
+  <si>
+    <t>47,4868</t>
+  </si>
+  <si>
+    <t>0,0900</t>
+  </si>
+  <si>
+    <t>6,84</t>
+  </si>
+  <si>
+    <t>669,01</t>
+  </si>
+  <si>
+    <t>1,91311</t>
+  </si>
+  <si>
+    <t>56,99</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>0,120000</t>
+  </si>
+  <si>
+    <t>76,336(6)</t>
+  </si>
+  <si>
     <t>0,10(2)</t>
-  </si>
-  <si>
-    <t>0,11(1)</t>
-  </si>
-  <si>
-    <t>1,09</t>
-  </si>
-  <si>
-    <t>0,14(1)</t>
-  </si>
-  <si>
-    <t>0,118(9)</t>
-  </si>
-  <si>
-    <t>0,15(2)</t>
-  </si>
-  <si>
-    <t>0,0720</t>
-  </si>
-  <si>
-    <t>0,096000</t>
-  </si>
-  <si>
-    <t>152(14)</t>
-  </si>
-  <si>
-    <t>7,82</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>15,0002</t>
-  </si>
-  <si>
-    <t>37,41</t>
-  </si>
-  <si>
-    <t>3797,06</t>
-  </si>
-  <si>
-    <t>5,90142</t>
-  </si>
-  <si>
-    <t>389,72</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-900-7375</t>
-  </si>
-  <si>
-    <t>4,14</t>
-  </si>
-  <si>
-    <t>16,746(3)</t>
-  </si>
-  <si>
-    <t>0,04(1)</t>
-  </si>
-  <si>
-    <t>21,76</t>
-  </si>
-  <si>
-    <t>2672,43</t>
-  </si>
-  <si>
-    <t>5,29006</t>
-  </si>
-  <si>
-    <t>363(61)</t>
-  </si>
-  <si>
-    <t>96-900-7375</t>
-  </si>
-  <si>
-    <t>0,059959</t>
-  </si>
-  <si>
-    <t>16,833(2)</t>
-  </si>
-  <si>
-    <t>0,070(4)</t>
-  </si>
-  <si>
-    <t>61,12</t>
-  </si>
-  <si>
-    <t>2652,92</t>
-  </si>
-  <si>
-    <t>5,26284</t>
-  </si>
-  <si>
-    <t>824(35)</t>
-  </si>
-  <si>
-    <t>8,75</t>
-  </si>
-  <si>
-    <t>0,074155</t>
-  </si>
-  <si>
-    <t>23,867(2)</t>
-  </si>
-  <si>
-    <t>0,072(7)</t>
-  </si>
-  <si>
-    <t>55,97</t>
-  </si>
-  <si>
-    <t>1792,74</t>
-  </si>
-  <si>
-    <t>3,72525</t>
-  </si>
-  <si>
-    <t>492(31)</t>
-  </si>
-  <si>
-    <t>5,23</t>
-  </si>
-  <si>
-    <t>0,113696</t>
-  </si>
-  <si>
-    <t>27,006(3)</t>
-  </si>
-  <si>
-    <t>37,17</t>
-  </si>
-  <si>
-    <t>1545,76</t>
-  </si>
-  <si>
-    <t>3,29895</t>
-  </si>
-  <si>
-    <t>296(22)</t>
-  </si>
-  <si>
-    <t>00-015-0861; 03-065-3883; 96-900-7375</t>
-  </si>
-  <si>
-    <t>3,15</t>
-  </si>
-  <si>
-    <t>0,125398</t>
-  </si>
-  <si>
-    <t>27,360(1)</t>
-  </si>
-  <si>
-    <t>0,078(4)</t>
-  </si>
-  <si>
-    <t>97,62</t>
-  </si>
-  <si>
-    <t>1518,37</t>
-  </si>
-  <si>
-    <t>3,25709</t>
-  </si>
-  <si>
-    <t>795(29)</t>
-  </si>
-  <si>
-    <t>8,45</t>
-  </si>
-  <si>
-    <t>0,122738</t>
-  </si>
-  <si>
-    <t>27,659(3)</t>
-  </si>
-  <si>
-    <t>86,27</t>
-  </si>
-  <si>
-    <t>1495,30</t>
-  </si>
-  <si>
-    <t>3,22257</t>
-  </si>
-  <si>
-    <t>466(23)</t>
-  </si>
-  <si>
-    <t>96-900-8581; 00-022-0733</t>
-  </si>
-  <si>
-    <t>4,95</t>
-  </si>
-  <si>
-    <t>0,184936</t>
-  </si>
-  <si>
-    <t>28,1699(6)</t>
-  </si>
-  <si>
-    <t>0,077(2)</t>
-  </si>
-  <si>
-    <t>218,91</t>
-  </si>
-  <si>
-    <t>1456,04</t>
-  </si>
-  <si>
-    <t>3,16526</t>
-  </si>
-  <si>
-    <t>1851(34)</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-901-3009; 96-900-7375</t>
-  </si>
-  <si>
-    <t>19,65</t>
-  </si>
-  <si>
-    <t>0,118284</t>
-  </si>
-  <si>
-    <t>31,1469(4)</t>
-  </si>
-  <si>
-    <t>0,092(1)</t>
-  </si>
-  <si>
-    <t>463,71</t>
-  </si>
-  <si>
-    <t>1237,79</t>
-  </si>
-  <si>
-    <t>2,86918</t>
-  </si>
-  <si>
-    <t>3590(32)</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-901-1650; 03-065-3883; 96-900-7375</t>
-  </si>
-  <si>
-    <t>38,12</t>
-  </si>
-  <si>
-    <t>0,129170</t>
-  </si>
-  <si>
-    <t>32,1930(8)</t>
-  </si>
-  <si>
-    <t>0,076(1)</t>
-  </si>
-  <si>
-    <t>142,66</t>
-  </si>
-  <si>
-    <t>1169,37</t>
-  </si>
-  <si>
-    <t>2,77829</t>
-  </si>
-  <si>
-    <t>1191(20)</t>
-  </si>
-  <si>
-    <t>00-015-0861; 01-085-0567; 96-900-7375</t>
-  </si>
-  <si>
-    <t>12,64</t>
-  </si>
-  <si>
-    <t>0,119828</t>
-  </si>
-  <si>
-    <t>33,104(2)</t>
-  </si>
-  <si>
-    <t>0,082(6)</t>
-  </si>
-  <si>
-    <t>49,89</t>
-  </si>
-  <si>
-    <t>1115,69</t>
-  </si>
-  <si>
-    <t>2,70389</t>
-  </si>
-  <si>
-    <t>444(22)</t>
-  </si>
-  <si>
-    <t>4,72</t>
-  </si>
-  <si>
-    <t>0,112251</t>
-  </si>
-  <si>
-    <t>34,0781(9)</t>
-  </si>
-  <si>
-    <t>0,078(3)</t>
-  </si>
-  <si>
-    <t>104,42</t>
-  </si>
-  <si>
-    <t>1066,09</t>
-  </si>
-  <si>
-    <t>2,62880</t>
-  </si>
-  <si>
-    <t>906(25)</t>
-  </si>
-  <si>
-    <t>00-015-0861; 00-022-0733; 96-900-7375</t>
-  </si>
-  <si>
-    <t>9,62</t>
-  </si>
-  <si>
-    <t>0,115264</t>
-  </si>
-  <si>
-    <t>35,6068(8)</t>
-  </si>
-  <si>
-    <t>0,104(3)</t>
-  </si>
-  <si>
-    <t>147,44</t>
-  </si>
-  <si>
-    <t>1009,11</t>
-  </si>
-  <si>
-    <t>2,51936</t>
-  </si>
-  <si>
-    <t>1128(20)</t>
-  </si>
-  <si>
-    <t>11,97</t>
-  </si>
-  <si>
-    <t>0,130759</t>
-  </si>
-  <si>
-    <t>37,990(1)</t>
-  </si>
-  <si>
-    <t>0,111(3)</t>
-  </si>
-  <si>
-    <t>142,29</t>
-  </si>
-  <si>
-    <t>910,83</t>
-  </si>
-  <si>
-    <t>2,36661</t>
-  </si>
-  <si>
-    <t>981(24)</t>
-  </si>
-  <si>
-    <t>10,42</t>
-  </si>
-  <si>
-    <t>0,144987</t>
-  </si>
-  <si>
-    <t>38,7952(9)</t>
-  </si>
-  <si>
-    <t>0,115(2)</t>
-  </si>
-  <si>
-    <t>194,94</t>
-  </si>
-  <si>
-    <t>883,09</t>
-  </si>
-  <si>
-    <t>2,31933</t>
-  </si>
-  <si>
-    <t>1308(23)</t>
-  </si>
-  <si>
-    <t>13,88</t>
-  </si>
-  <si>
-    <t>0,149085</t>
-  </si>
-  <si>
-    <t>39,07(1)</t>
-  </si>
-  <si>
-    <t>0,07(4)</t>
-  </si>
-  <si>
-    <t>10,21</t>
-  </si>
-  <si>
-    <t>873,87</t>
-  </si>
-  <si>
-    <t>2,30339</t>
-  </si>
-  <si>
-    <t>119(676)</t>
-  </si>
-  <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>0,085506</t>
-  </si>
-  <si>
-    <t>39,451(5)</t>
-  </si>
-  <si>
-    <t>861,75</t>
-  </si>
-  <si>
-    <t>2,28230</t>
-  </si>
-  <si>
-    <t>0(690)</t>
-  </si>
-  <si>
-    <t>0,094547</t>
-  </si>
-  <si>
-    <t>40,3560(4)</t>
-  </si>
-  <si>
-    <t>0,3754(9)</t>
-  </si>
-  <si>
-    <t>4795,79</t>
-  </si>
-  <si>
-    <t>833,96</t>
-  </si>
-  <si>
-    <t>2,23315</t>
-  </si>
-  <si>
-    <t>9417(27)</t>
-  </si>
-  <si>
-    <t>0,509251</t>
-  </si>
-  <si>
-    <t>41,326(3)</t>
-  </si>
-  <si>
-    <t>0,164(9)</t>
-  </si>
-  <si>
-    <t>83,91</t>
-  </si>
-  <si>
-    <t>806,22</t>
-  </si>
-  <si>
-    <t>2,18297</t>
-  </si>
-  <si>
-    <t>385(18)</t>
-  </si>
-  <si>
-    <t>4,09</t>
-  </si>
-  <si>
-    <t>0,218042</t>
-  </si>
-  <si>
-    <t>0,13(3)</t>
-  </si>
-  <si>
-    <t>8,64</t>
-  </si>
-  <si>
-    <t>795,43</t>
-  </si>
-  <si>
-    <t>2,16311</t>
-  </si>
-  <si>
-    <t>50(12)</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>0,173537</t>
-  </si>
-  <si>
-    <t>44,935(2)</t>
-  </si>
-  <si>
-    <t>0,157(6)</t>
-  </si>
-  <si>
-    <t>111,31</t>
-  </si>
-  <si>
-    <t>718,69</t>
-  </si>
-  <si>
-    <t>2,01567</t>
-  </si>
-  <si>
-    <t>533(18)</t>
-  </si>
-  <si>
-    <t>5,66</t>
-  </si>
-  <si>
-    <t>0,208909</t>
-  </si>
-  <si>
-    <t>45,103(4)</t>
-  </si>
-  <si>
-    <t>0,063(8)</t>
-  </si>
-  <si>
-    <t>23,38</t>
-  </si>
-  <si>
-    <t>715,14</t>
-  </si>
-  <si>
-    <t>2,00853</t>
-  </si>
-  <si>
-    <t>283(46)</t>
-  </si>
-  <si>
-    <t>3,01</t>
-  </si>
-  <si>
-    <t>0,082573</t>
-  </si>
-  <si>
-    <t>45,251(2)</t>
-  </si>
-  <si>
-    <t>0,036(6)</t>
-  </si>
-  <si>
-    <t>712,04</t>
-  </si>
-  <si>
-    <t>2,00230</t>
-  </si>
-  <si>
-    <t>218(36)</t>
-  </si>
-  <si>
-    <t>2,32</t>
-  </si>
-  <si>
-    <t>0,046763</t>
-  </si>
-  <si>
-    <t>45,42(1)</t>
-  </si>
-  <si>
-    <t>0,17(3)</t>
-  </si>
-  <si>
-    <t>44,82</t>
-  </si>
-  <si>
-    <t>708,65</t>
-  </si>
-  <si>
-    <t>1,99544</t>
-  </si>
-  <si>
-    <t>204(29)</t>
-  </si>
-  <si>
-    <t>2,16</t>
-  </si>
-  <si>
-    <t>0,220159</t>
-  </si>
-  <si>
-    <t>45,562(2)</t>
-  </si>
-  <si>
-    <t>0,079(8)</t>
-  </si>
-  <si>
-    <t>62,66</t>
-  </si>
-  <si>
-    <t>705,65</t>
-  </si>
-  <si>
-    <t>1,98936</t>
-  </si>
-  <si>
-    <t>603(54)</t>
-  </si>
-  <si>
-    <t>6,40</t>
-  </si>
-  <si>
-    <t>0,103977</t>
-  </si>
-  <si>
-    <t>45,982(5)</t>
-  </si>
-  <si>
-    <t>0,11(2)</t>
-  </si>
-  <si>
-    <t>22,94</t>
-  </si>
-  <si>
-    <t>697,24</t>
-  </si>
-  <si>
-    <t>1,97217</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>0,151181</t>
-  </si>
-  <si>
-    <t>48,925(8)</t>
-  </si>
-  <si>
-    <t>644,59</t>
-  </si>
-  <si>
-    <t>1,86019</t>
-  </si>
-  <si>
-    <t>71(9)</t>
-  </si>
-  <si>
-    <t>0,76</t>
-  </si>
-  <si>
-    <t>0,109831</t>
-  </si>
-  <si>
-    <t>49,62(1)</t>
-  </si>
-  <si>
-    <t>0,08(4)</t>
-  </si>
-  <si>
-    <t>5,80</t>
-  </si>
-  <si>
-    <t>633,65</t>
-  </si>
-  <si>
-    <t>1,83590</t>
-  </si>
-  <si>
-    <t>54(12)</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>0,107909</t>
-  </si>
-  <si>
-    <t>51,034(4)</t>
-  </si>
-  <si>
-    <t>28,71</t>
-  </si>
-  <si>
-    <t>612,68</t>
-  </si>
-  <si>
-    <t>1,78815</t>
-  </si>
-  <si>
-    <t>191(13)</t>
-  </si>
-  <si>
-    <t>2,02</t>
-  </si>
-  <si>
-    <t>0,150533</t>
-  </si>
-  <si>
-    <t>51,9247(7)</t>
-  </si>
-  <si>
-    <t>0,162(2)</t>
-  </si>
-  <si>
-    <t>402,92</t>
-  </si>
-  <si>
-    <t>600,44</t>
-  </si>
-  <si>
-    <t>1,75956</t>
-  </si>
-  <si>
-    <t>1961(17)</t>
-  </si>
-  <si>
-    <t>20,82</t>
-  </si>
-  <si>
-    <t>0,205507</t>
-  </si>
-  <si>
-    <t>52,153(5)</t>
-  </si>
-  <si>
-    <t>0,12(2)</t>
-  </si>
-  <si>
-    <t>27,75</t>
-  </si>
-  <si>
-    <t>597,41</t>
-  </si>
-  <si>
-    <t>1,75239</t>
-  </si>
-  <si>
-    <t>182(17)</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-900-8581; 96-901-1650; 96-900-7375</t>
-  </si>
-  <si>
-    <t>1,93</t>
-  </si>
-  <si>
-    <t>0,152291</t>
-  </si>
-  <si>
-    <t>53,993(3)</t>
-  </si>
-  <si>
-    <t>45,55</t>
-  </si>
-  <si>
-    <t>574,45</t>
-  </si>
-  <si>
-    <t>1,69693</t>
-  </si>
-  <si>
-    <t>257(12)</t>
-  </si>
-  <si>
-    <t>2,73</t>
-  </si>
-  <si>
-    <t>0,177429</t>
-  </si>
-  <si>
-    <t>55,33(1)</t>
-  </si>
-  <si>
-    <t>8,65</t>
-  </si>
-  <si>
-    <t>559,20</t>
-  </si>
-  <si>
-    <t>1,65896</t>
-  </si>
-  <si>
-    <t>52(8)</t>
-  </si>
-  <si>
-    <t>96-901-1650; 03-065-3883; 96-900-7375</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>0,166478</t>
-  </si>
-  <si>
-    <t>58,158(3)</t>
-  </si>
-  <si>
-    <t>0,226(6)</t>
-  </si>
-  <si>
-    <t>128,33</t>
-  </si>
-  <si>
-    <t>530,51</t>
-  </si>
-  <si>
-    <t>1,58494</t>
-  </si>
-  <si>
-    <t>422(12)</t>
-  </si>
-  <si>
-    <t>4,48</t>
-  </si>
-  <si>
-    <t>0,304233</t>
-  </si>
-  <si>
-    <t>61,121(2)</t>
-  </si>
-  <si>
-    <t>0,020(3)</t>
-  </si>
-  <si>
-    <t>4,84</t>
-  </si>
-  <si>
-    <t>504,39</t>
-  </si>
-  <si>
-    <t>1,51500</t>
-  </si>
-  <si>
-    <t>181(7)</t>
-  </si>
-  <si>
-    <t>01-085-0567; 96-901-1650; 96-900-7375</t>
-  </si>
-  <si>
-    <t>1,92</t>
-  </si>
-  <si>
-    <t>0,026755</t>
-  </si>
-  <si>
-    <t>63,242(8)</t>
-  </si>
-  <si>
-    <t>0,22(2)</t>
-  </si>
-  <si>
-    <t>31,67</t>
-  </si>
-  <si>
-    <t>487,63</t>
-  </si>
-  <si>
-    <t>1,46920</t>
-  </si>
-  <si>
-    <t>110(9)</t>
-  </si>
-  <si>
-    <t>00-022-0733; 96-900-7375</t>
-  </si>
-  <si>
-    <t>1,16</t>
-  </si>
-  <si>
-    <t>0,288959</t>
-  </si>
-  <si>
-    <t>66,185(6)</t>
-  </si>
-  <si>
-    <t>13,43</t>
-  </si>
-  <si>
-    <t>466,32</t>
-  </si>
-  <si>
-    <t>1,41082</t>
-  </si>
-  <si>
-    <t>95(12)</t>
-  </si>
-  <si>
-    <t>96-901-3009; 96-900-7375</t>
-  </si>
-  <si>
-    <t>1,00</t>
-  </si>
-  <si>
-    <t>0,141915</t>
-  </si>
-  <si>
-    <t>69,023(6)</t>
-  </si>
-  <si>
-    <t>19,94</t>
-  </si>
-  <si>
-    <t>447,33</t>
-  </si>
-  <si>
-    <t>1,35959</t>
-  </si>
-  <si>
-    <t>103(9)</t>
-  </si>
-  <si>
-    <t>03-065-3883; 96-900-7375</t>
-  </si>
-  <si>
-    <t>0,193647</t>
-  </si>
-  <si>
-    <t>71,759(4)</t>
-  </si>
-  <si>
-    <t>22,20</t>
-  </si>
-  <si>
-    <t>429,90</t>
-  </si>
-  <si>
-    <t>1,31431</t>
-  </si>
-  <si>
-    <t>147(14)</t>
-  </si>
-  <si>
-    <t>1,56</t>
-  </si>
-  <si>
-    <t>0,151518</t>
-  </si>
-  <si>
-    <t>73,492(4)</t>
-  </si>
-  <si>
-    <t>0,764(9)</t>
-  </si>
-  <si>
-    <t>566,28</t>
-  </si>
-  <si>
-    <t>419,13</t>
-  </si>
-  <si>
-    <t>1,28755</t>
-  </si>
-  <si>
-    <t>559(8)</t>
-  </si>
-  <si>
-    <t>5,94</t>
-  </si>
-  <si>
-    <t>1,012227</t>
-  </si>
-  <si>
-    <t>76(976)</t>
-  </si>
-  <si>
-    <t>1(8307)</t>
-  </si>
-  <si>
-    <t>405,99</t>
-  </si>
-  <si>
-    <t>1,25650</t>
-  </si>
-  <si>
-    <t>1(913)</t>
-  </si>
-  <si>
-    <t>0,01</t>
-  </si>
-  <si>
-    <t>1,488329</t>
-  </si>
-  <si>
-    <t>76,336(6)</t>
   </si>
   <si>
     <t>11,03</t>
@@ -1219,6 +1255,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1538,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4B8A9B-7994-4D7C-8BA3-BE0666BFC9CE}">
-  <dimension ref="A1:W43"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -1617,43 +1657,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>50</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" t="s">
-        <v>53</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="U2" t="s">
         <v>26</v>
@@ -1662,7 +1702,7 @@
         <v>27</v>
       </c>
       <c r="W2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -1670,43 +1710,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="P3" t="s">
         <v>57</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P3" t="s">
-        <v>61</v>
       </c>
       <c r="Q3" t="s">
         <v>28</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" t="s">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="T3" t="s">
         <v>30</v>
@@ -1718,7 +1755,7 @@
         <v>27</v>
       </c>
       <c r="W3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -1726,34 +1763,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" t="s">
         <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" t="s">
-        <v>68</v>
-      </c>
-      <c r="P4" t="s">
-        <v>69</v>
       </c>
       <c r="Q4" t="s">
         <v>28</v>
@@ -1762,10 +1799,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="U4" t="s">
         <v>29</v>
@@ -1774,7 +1811,7 @@
         <v>27</v>
       </c>
       <c r="W4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -1782,34 +1819,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P5" t="s">
         <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" t="s">
-        <v>75</v>
-      </c>
-      <c r="O5" t="s">
-        <v>76</v>
-      </c>
-      <c r="P5" t="s">
-        <v>77</v>
       </c>
       <c r="Q5" t="s">
         <v>28</v>
@@ -1818,10 +1855,10 @@
         <v>1</v>
       </c>
       <c r="S5" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="U5" t="s">
         <v>29</v>
@@ -1830,7 +1867,7 @@
         <v>27</v>
       </c>
       <c r="W5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -1838,10 +1875,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -1853,19 +1890,19 @@
         <v>24</v>
       </c>
       <c r="L6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="s">
         <v>28</v>
@@ -1874,10 +1911,10 @@
         <v>1</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
+        <v>352</v>
       </c>
       <c r="T6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="U6" t="s">
         <v>29</v>
@@ -1886,7 +1923,7 @@
         <v>27</v>
       </c>
       <c r="W6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -1894,10 +1931,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1909,19 +1946,19 @@
         <v>24</v>
       </c>
       <c r="L7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="O7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="Q7" t="s">
         <v>28</v>
@@ -1930,10 +1967,10 @@
         <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="U7" t="s">
         <v>29</v>
@@ -1942,7 +1979,7 @@
         <v>27</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -1950,10 +1987,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1965,19 +2002,19 @@
         <v>24</v>
       </c>
       <c r="L8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="O8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q8" t="s">
         <v>28</v>
@@ -1986,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="S8" t="s">
-        <v>101</v>
+        <v>353</v>
       </c>
       <c r="T8" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="U8" t="s">
         <v>29</v>
@@ -1998,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="W8" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -2006,10 +2043,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -2021,19 +2058,19 @@
         <v>24</v>
       </c>
       <c r="L9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="Q9" t="s">
         <v>28</v>
@@ -2042,10 +2079,10 @@
         <v>1</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>352</v>
       </c>
       <c r="T9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U9" t="s">
         <v>29</v>
@@ -2054,7 +2091,7 @@
         <v>27</v>
       </c>
       <c r="W9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -2062,10 +2099,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -2077,19 +2114,19 @@
         <v>24</v>
       </c>
       <c r="L10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="P10" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q10" t="s">
         <v>28</v>
@@ -2098,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="S10" t="s">
-        <v>119</v>
+        <v>352</v>
       </c>
       <c r="T10" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="U10" t="s">
         <v>29</v>
@@ -2110,7 +2147,7 @@
         <v>27</v>
       </c>
       <c r="W10" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -2118,10 +2155,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -2133,19 +2170,19 @@
         <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="P11" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="Q11" t="s">
         <v>28</v>
@@ -2154,10 +2191,10 @@
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>128</v>
+        <v>352</v>
       </c>
       <c r="T11" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="U11" t="s">
         <v>29</v>
@@ -2166,7 +2203,7 @@
         <v>27</v>
       </c>
       <c r="W11" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -2174,10 +2211,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -2189,19 +2226,19 @@
         <v>24</v>
       </c>
       <c r="L12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="M12" t="s">
         <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O12" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="P12" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="Q12" t="s">
         <v>28</v>
@@ -2210,10 +2247,10 @@
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T12" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="U12" t="s">
         <v>29</v>
@@ -2222,7 +2259,7 @@
         <v>27</v>
       </c>
       <c r="W12" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -2230,10 +2267,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
@@ -2245,19 +2282,19 @@
         <v>24</v>
       </c>
       <c r="L13" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="M13" t="s">
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="O13" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="P13" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="Q13" t="s">
         <v>28</v>
@@ -2266,10 +2303,10 @@
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="T13" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="U13" t="s">
         <v>29</v>
@@ -2278,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="W13" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -2286,10 +2323,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>364</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>365</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -2301,40 +2338,37 @@
         <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>150</v>
+        <v>366</v>
       </c>
       <c r="M14" t="s">
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>151</v>
+        <v>367</v>
       </c>
       <c r="O14" t="s">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>28</v>
+        <v>369</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>54</v>
+        <v>354</v>
       </c>
       <c r="T14" t="s">
-        <v>154</v>
+        <v>370</v>
       </c>
       <c r="U14" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="V14" t="s">
         <v>27</v>
       </c>
       <c r="W14" t="s">
-        <v>155</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2342,10 +2376,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -2357,19 +2391,19 @@
         <v>24</v>
       </c>
       <c r="L15" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s">
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="O15" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="P15" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="s">
         <v>28</v>
@@ -2378,10 +2412,10 @@
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="T15" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="U15" t="s">
         <v>29</v>
@@ -2390,7 +2424,7 @@
         <v>27</v>
       </c>
       <c r="W15" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2398,10 +2432,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D16" t="s">
         <v>23</v>
@@ -2413,19 +2447,19 @@
         <v>24</v>
       </c>
       <c r="L16" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="M16" t="s">
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="O16" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="Q16" t="s">
         <v>28</v>
@@ -2434,10 +2468,10 @@
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>54</v>
+        <v>354</v>
       </c>
       <c r="T16" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="U16" t="s">
         <v>29</v>
@@ -2446,7 +2480,7 @@
         <v>27</v>
       </c>
       <c r="W16" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2454,10 +2488,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
@@ -2469,19 +2503,19 @@
         <v>24</v>
       </c>
       <c r="L17" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s">
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="O17" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="Q17" t="s">
         <v>28</v>
@@ -2490,10 +2524,10 @@
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="T17" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="U17" t="s">
         <v>29</v>
@@ -2502,7 +2536,7 @@
         <v>27</v>
       </c>
       <c r="W17" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2510,10 +2544,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -2525,19 +2559,19 @@
         <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="M18" t="s">
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="Q18" t="s">
         <v>28</v>
@@ -2546,10 +2580,10 @@
         <v>1</v>
       </c>
       <c r="S18" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T18" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="U18" t="s">
         <v>29</v>
@@ -2558,7 +2592,7 @@
         <v>27</v>
       </c>
       <c r="W18" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2566,10 +2600,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
@@ -2581,19 +2615,19 @@
         <v>24</v>
       </c>
       <c r="L19" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="O19" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="P19" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="Q19" t="s">
         <v>28</v>
@@ -2602,10 +2636,10 @@
         <v>1</v>
       </c>
       <c r="S19" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
       <c r="T19" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="U19" t="s">
         <v>29</v>
@@ -2614,7 +2648,7 @@
         <v>27</v>
       </c>
       <c r="W19" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -2622,10 +2656,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
@@ -2637,31 +2671,28 @@
         <v>24</v>
       </c>
       <c r="L20" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="M20" t="s">
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="O20" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="P20" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="s">
         <v>28</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
-      </c>
-      <c r="S20" t="s">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>198</v>
+        <v>32</v>
       </c>
       <c r="U20" t="s">
         <v>29</v>
@@ -2670,7 +2701,7 @@
         <v>27</v>
       </c>
       <c r="W20" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -2678,10 +2709,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
@@ -2693,19 +2724,19 @@
         <v>24</v>
       </c>
       <c r="L21" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="M21" t="s">
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="O21" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="P21" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="Q21" t="s">
         <v>28</v>
@@ -2714,10 +2745,10 @@
         <v>1</v>
       </c>
       <c r="S21" t="s">
-        <v>85</v>
+        <v>352</v>
       </c>
       <c r="T21" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="U21" t="s">
         <v>29</v>
@@ -2726,7 +2757,7 @@
         <v>27</v>
       </c>
       <c r="W21" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -2734,10 +2765,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D22" t="s">
         <v>23</v>
@@ -2749,19 +2780,19 @@
         <v>24</v>
       </c>
       <c r="L22" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s">
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="O22" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="Q22" t="s">
         <v>28</v>
@@ -2770,10 +2801,10 @@
         <v>1</v>
       </c>
       <c r="S22" t="s">
-        <v>85</v>
+        <v>352</v>
       </c>
       <c r="T22" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="U22" t="s">
         <v>29</v>
@@ -2782,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="W22" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2790,10 +2821,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
@@ -2805,19 +2836,19 @@
         <v>24</v>
       </c>
       <c r="L23" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="M23" t="s">
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="O23" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="Q23" t="s">
         <v>28</v>
@@ -2826,10 +2857,10 @@
         <v>1</v>
       </c>
       <c r="S23" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="T23" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="U23" t="s">
         <v>29</v>
@@ -2838,7 +2869,7 @@
         <v>27</v>
       </c>
       <c r="W23" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2846,10 +2877,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
@@ -2861,19 +2892,19 @@
         <v>24</v>
       </c>
       <c r="L24" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="M24" t="s">
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="O24" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="Q24" t="s">
         <v>28</v>
@@ -2882,10 +2913,10 @@
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="T24" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="U24" t="s">
         <v>29</v>
@@ -2894,7 +2925,7 @@
         <v>27</v>
       </c>
       <c r="W24" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -2902,10 +2933,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C25" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
@@ -2917,19 +2948,19 @@
         <v>24</v>
       </c>
       <c r="L25" t="s">
-        <v>232</v>
+        <v>163</v>
       </c>
       <c r="M25" t="s">
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="O25" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="P25" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
@@ -2938,10 +2969,10 @@
         <v>1</v>
       </c>
       <c r="S25" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T25" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="U25" t="s">
         <v>29</v>
@@ -2950,7 +2981,7 @@
         <v>27</v>
       </c>
       <c r="W25" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -2958,10 +2989,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="C26" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
@@ -2973,19 +3004,19 @@
         <v>24</v>
       </c>
       <c r="L26" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="M26" t="s">
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="O26" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="P26" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="Q26" t="s">
         <v>28</v>
@@ -2994,10 +3025,10 @@
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T26" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="U26" t="s">
         <v>29</v>
@@ -3006,7 +3037,7 @@
         <v>27</v>
       </c>
       <c r="W26" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -3014,10 +3045,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C27" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
@@ -3029,19 +3060,19 @@
         <v>24</v>
       </c>
       <c r="L27" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="M27" t="s">
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="O27" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="P27" t="s">
-        <v>46</v>
+        <v>232</v>
       </c>
       <c r="Q27" t="s">
         <v>28</v>
@@ -3050,10 +3081,10 @@
         <v>1</v>
       </c>
       <c r="S27" t="s">
-        <v>31</v>
+        <v>352</v>
       </c>
       <c r="T27" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="U27" t="s">
         <v>29</v>
@@ -3062,7 +3093,7 @@
         <v>27</v>
       </c>
       <c r="W27" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3070,10 +3101,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="D28" t="s">
         <v>23</v>
@@ -3085,31 +3116,28 @@
         <v>24</v>
       </c>
       <c r="L28" t="s">
-        <v>47</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s">
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="O28" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>43</v>
       </c>
       <c r="Q28" t="s">
         <v>28</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
-      </c>
-      <c r="S28" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="U28" t="s">
         <v>29</v>
@@ -3118,7 +3146,7 @@
         <v>27</v>
       </c>
       <c r="W28" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -3126,10 +3154,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>259</v>
+        <v>372</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
@@ -3141,40 +3169,37 @@
         <v>24</v>
       </c>
       <c r="L29" t="s">
-        <v>261</v>
+        <v>374</v>
       </c>
       <c r="M29" t="s">
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="O29" t="s">
-        <v>263</v>
+        <v>376</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>28</v>
+        <v>377</v>
       </c>
       <c r="R29" t="b">
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>54</v>
+        <v>354</v>
       </c>
       <c r="T29" t="s">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="U29" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="V29" t="s">
         <v>27</v>
       </c>
       <c r="W29" t="s">
-        <v>266</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -3182,10 +3207,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
@@ -3197,19 +3222,19 @@
         <v>24</v>
       </c>
       <c r="L30" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
       <c r="M30" t="s">
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="O30" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="P30" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="Q30" t="s">
         <v>28</v>
@@ -3218,10 +3243,10 @@
         <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T30" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="U30" t="s">
         <v>29</v>
@@ -3230,7 +3255,7 @@
         <v>27</v>
       </c>
       <c r="W30" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3238,10 +3263,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="C31" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
@@ -3253,19 +3278,19 @@
         <v>24</v>
       </c>
       <c r="L31" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="M31" t="s">
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="O31" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="P31" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="Q31" t="s">
         <v>28</v>
@@ -3274,10 +3299,10 @@
         <v>1</v>
       </c>
       <c r="S31" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="T31" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="U31" t="s">
         <v>29</v>
@@ -3286,7 +3311,7 @@
         <v>27</v>
       </c>
       <c r="W31" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3294,10 +3319,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="C32" t="s">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
         <v>23</v>
@@ -3309,19 +3334,19 @@
         <v>24</v>
       </c>
       <c r="L32" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="M32" t="s">
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="O32" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="P32" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
@@ -3330,10 +3355,10 @@
         <v>1</v>
       </c>
       <c r="S32" t="s">
-        <v>288</v>
+        <v>352</v>
       </c>
       <c r="T32" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="U32" t="s">
         <v>29</v>
@@ -3342,7 +3367,7 @@
         <v>27</v>
       </c>
       <c r="W32" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3350,10 +3375,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>264</v>
       </c>
       <c r="D33" t="s">
         <v>23</v>
@@ -3365,19 +3390,19 @@
         <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="M33" t="s">
         <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="O33" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="P33" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="Q33" t="s">
         <v>28</v>
@@ -3386,10 +3411,10 @@
         <v>1</v>
       </c>
       <c r="S33" t="s">
-        <v>128</v>
+        <v>352</v>
       </c>
       <c r="T33" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="U33" t="s">
         <v>29</v>
@@ -3398,7 +3423,7 @@
         <v>27</v>
       </c>
       <c r="W33" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -3406,10 +3431,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -3421,19 +3446,19 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="M34" t="s">
         <v>25</v>
       </c>
       <c r="N34" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="O34" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="P34" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="Q34" t="s">
         <v>28</v>
@@ -3442,10 +3467,10 @@
         <v>1</v>
       </c>
       <c r="S34" t="s">
-        <v>303</v>
+        <v>352</v>
       </c>
       <c r="T34" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="U34" t="s">
         <v>29</v>
@@ -3454,7 +3479,7 @@
         <v>27</v>
       </c>
       <c r="W34" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -3462,10 +3487,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="C35" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
@@ -3477,19 +3502,19 @@
         <v>24</v>
       </c>
       <c r="L35" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="M35" t="s">
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="O35" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="P35" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="Q35" t="s">
         <v>28</v>
@@ -3498,10 +3523,10 @@
         <v>1</v>
       </c>
       <c r="S35" t="s">
-        <v>128</v>
+        <v>352</v>
       </c>
       <c r="T35" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="U35" t="s">
         <v>29</v>
@@ -3510,7 +3535,7 @@
         <v>27</v>
       </c>
       <c r="W35" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -3518,10 +3543,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="C36" t="s">
-        <v>315</v>
+        <v>189</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -3533,31 +3558,28 @@
         <v>24</v>
       </c>
       <c r="L36" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="M36" t="s">
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="O36" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="P36" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="Q36" t="s">
         <v>28</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
-      </c>
-      <c r="S36" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="U36" t="s">
         <v>29</v>
@@ -3566,7 +3588,7 @@
         <v>27</v>
       </c>
       <c r="W36" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -3574,10 +3596,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -3589,19 +3611,19 @@
         <v>24</v>
       </c>
       <c r="L37" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s">
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="O37" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="P37" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="Q37" t="s">
         <v>28</v>
@@ -3610,10 +3632,10 @@
         <v>1</v>
       </c>
       <c r="S37" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="T37" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="U37" t="s">
         <v>29</v>
@@ -3622,7 +3644,7 @@
         <v>27</v>
       </c>
       <c r="W37" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -3630,10 +3652,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="C38" t="s">
-        <v>247</v>
+        <v>302</v>
       </c>
       <c r="D38" t="s">
         <v>23</v>
@@ -3645,31 +3667,28 @@
         <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s">
         <v>25</v>
       </c>
       <c r="N38" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="O38" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="P38" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="Q38" t="s">
         <v>28</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="s">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="U38" t="s">
         <v>29</v>
@@ -3678,7 +3697,7 @@
         <v>27</v>
       </c>
       <c r="W38" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -3686,10 +3705,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
@@ -3701,31 +3720,28 @@
         <v>24</v>
       </c>
       <c r="L39" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s">
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="O39" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="P39" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="Q39" t="s">
         <v>28</v>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>40</v>
+        <v>315</v>
       </c>
       <c r="U39" t="s">
         <v>29</v>
@@ -3734,7 +3750,7 @@
         <v>27</v>
       </c>
       <c r="W39" t="s">
-        <v>346</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -3742,10 +3758,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>356</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -3757,40 +3773,37 @@
         <v>24</v>
       </c>
       <c r="L40" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="M40" t="s">
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="O40" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="P40" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>28</v>
+        <v>360</v>
       </c>
       <c r="R40" t="b">
         <v>1</v>
       </c>
       <c r="S40" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="T40" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="U40" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="V40" t="s">
         <v>27</v>
       </c>
       <c r="W40" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -3798,10 +3811,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="C41" t="s">
-        <v>355</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
@@ -3813,31 +3826,28 @@
         <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="M41" t="s">
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="O41" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="P41" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
       <c r="Q41" t="s">
         <v>28</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
-      </c>
-      <c r="S41" t="s">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="U41" t="s">
         <v>29</v>
@@ -3846,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="W41" t="s">
-        <v>361</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -3854,10 +3864,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="C42" t="s">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
@@ -3869,31 +3879,28 @@
         <v>24</v>
       </c>
       <c r="L42" t="s">
-        <v>48</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s">
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="O42" t="s">
-        <v>365</v>
+        <v>327</v>
       </c>
       <c r="P42" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="Q42" t="s">
         <v>28</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>367</v>
+        <v>37</v>
       </c>
       <c r="U42" t="s">
         <v>29</v>
@@ -3902,7 +3909,7 @@
         <v>27</v>
       </c>
       <c r="W42" t="s">
-        <v>368</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -3910,10 +3917,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
         <v>23</v>
@@ -3925,31 +3932,28 @@
         <v>24</v>
       </c>
       <c r="L43" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s">
         <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="O43" t="s">
-        <v>372</v>
+        <v>333</v>
       </c>
       <c r="P43" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="Q43" t="s">
         <v>28</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="U43" t="s">
         <v>29</v>
@@ -3958,7 +3962,169 @@
         <v>27</v>
       </c>
       <c r="W43" t="s">
-        <v>375</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" t="s">
+        <v>338</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" t="s">
+        <v>339</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+      <c r="N44" t="s">
+        <v>340</v>
+      </c>
+      <c r="O44" t="s">
+        <v>341</v>
+      </c>
+      <c r="P44" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>28</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="s">
+        <v>343</v>
+      </c>
+      <c r="U44" t="s">
+        <v>29</v>
+      </c>
+      <c r="V44" t="s">
+        <v>27</v>
+      </c>
+      <c r="W44" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>345</v>
+      </c>
+      <c r="C45" t="s">
+        <v>346</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" t="s">
+        <v>45</v>
+      </c>
+      <c r="M45" t="s">
+        <v>25</v>
+      </c>
+      <c r="N45" t="s">
+        <v>347</v>
+      </c>
+      <c r="O45" t="s">
+        <v>348</v>
+      </c>
+      <c r="P45" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>28</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="s">
+        <v>350</v>
+      </c>
+      <c r="U45" t="s">
+        <v>29</v>
+      </c>
+      <c r="V45" t="s">
+        <v>27</v>
+      </c>
+      <c r="W45" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>380</v>
+      </c>
+      <c r="C46" t="s">
+        <v>381</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" t="s">
+        <v>382</v>
+      </c>
+      <c r="M46" t="s">
+        <v>25</v>
+      </c>
+      <c r="N46" t="s">
+        <v>383</v>
+      </c>
+      <c r="O46" t="s">
+        <v>384</v>
+      </c>
+      <c r="P46" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>28</v>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="s">
+        <v>353</v>
+      </c>
+      <c r="T46" t="s">
+        <v>386</v>
+      </c>
+      <c r="U46" t="s">
+        <v>29</v>
+      </c>
+      <c r="V46" t="s">
+        <v>27</v>
+      </c>
+      <c r="W46" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
